--- a/templates/template_inspec_excavadora.xlsx
+++ b/templates/template_inspec_excavadora.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Developer user\android\williApp\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elksi\Android\williApp\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A701536E-9EE5-475D-9963-A88D8841EB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E68D49F-0343-475C-AD20-61DE359B5043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FT-MANT-08" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
   </externalReferences>
   <definedNames>
     <definedName name="AÑO">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'FT-MANT-08'!$A$1:$P$32</definedName>
     <definedName name="Cargos">[1]Datos!$D$2:$D$39</definedName>
     <definedName name="CERT">#REF!</definedName>
     <definedName name="CREDITO">#REF!</definedName>
@@ -41,6 +40,7 @@
     <definedName name="MENSAJEERROR2">[2]Hoja1!$D$1</definedName>
     <definedName name="MES">#REF!</definedName>
     <definedName name="PLAZO">#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'FT-MANT-08'!$A$1:$P$32</definedName>
     <definedName name="TIPODEE">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="63">
   <si>
     <t>Señale su respuesta con una ´´X´´</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>OBSERVACIONES</t>
+  </si>
+  <si>
+    <t>CEDULA</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1375,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1440,6 +1443,30 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -1687,82 +1714,64 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="62">
@@ -2811,108 +2820,108 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="4.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="4.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.28515625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="45.42578125" style="1" customWidth="1"/>
-    <col min="14" max="15" width="4.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="6.85546875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="5.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.88671875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="4.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.5546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5546875" style="1" customWidth="1"/>
+    <col min="10" max="11" width="4.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.33203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="45.44140625" style="1" customWidth="1"/>
+    <col min="14" max="15" width="4.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="6.88671875" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" customHeight="1">
-      <c r="A1" s="74"/>
-      <c r="B1" s="75"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="26" t="s">
+      <c r="A1" s="82"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="28"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="36"/>
       <c r="M1" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="35" t="s">
+      <c r="N1" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="35"/>
-      <c r="P1" s="36"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44"/>
     </row>
     <row r="2" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A2" s="77"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="31"/>
+      <c r="A2" s="85"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="39"/>
       <c r="M2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="37">
+      <c r="N2" s="45">
         <v>9</v>
       </c>
-      <c r="O2" s="37"/>
-      <c r="P2" s="38"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="46"/>
     </row>
     <row r="3" spans="1:16" ht="25.5" customHeight="1">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="34"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="42"/>
       <c r="M3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="39">
+      <c r="N3" s="47">
         <v>45219</v>
       </c>
-      <c r="O3" s="39"/>
-      <c r="P3" s="40"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="48"/>
     </row>
     <row r="4" spans="1:16" ht="6.75" customHeight="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
-      <c r="M4" s="96"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="104"/>
       <c r="N4" s="13"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="84"/>
+      <c r="O4" s="91"/>
+      <c r="P4" s="92"/>
     </row>
     <row r="5" spans="1:16" ht="20.25" customHeight="1">
       <c r="A5" s="21"/>
@@ -2920,23 +2929,23 @@
       <c r="C5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="59"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="88" t="s">
+      <c r="D5" s="67"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="89"/>
-      <c r="K5" s="89"/>
-      <c r="L5" s="89"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="97"/>
       <c r="M5" s="24" t="s">
         <v>4</v>
       </c>
       <c r="N5" s="23"/>
-      <c r="O5" s="83"/>
-      <c r="P5" s="84"/>
+      <c r="O5" s="91"/>
+      <c r="P5" s="92"/>
     </row>
     <row r="6" spans="1:16" ht="20.25" customHeight="1">
       <c r="A6" s="21"/>
@@ -2944,23 +2953,23 @@
       <c r="C6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="93" t="s">
+      <c r="D6" s="67"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="101" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="94"/>
-      <c r="K6" s="94"/>
-      <c r="L6" s="94"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="102"/>
       <c r="M6" s="24" t="s">
         <v>4</v>
       </c>
       <c r="N6" s="2"/>
-      <c r="O6" s="83"/>
-      <c r="P6" s="84"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="92"/>
     </row>
     <row r="7" spans="1:16" ht="20.25" customHeight="1">
       <c r="A7" s="21"/>
@@ -2968,21 +2977,21 @@
       <c r="C7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="59"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="49" t="s">
+      <c r="D7" s="67"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
       <c r="M7" s="25"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="83"/>
-      <c r="P7" s="84"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="92"/>
     </row>
     <row r="8" spans="1:16" ht="20.25" customHeight="1">
       <c r="A8" s="21"/>
@@ -2990,23 +2999,23 @@
       <c r="C8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="59"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="41" t="s">
+      <c r="D8" s="67"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="50"/>
       <c r="M8" s="24" t="s">
         <v>4</v>
       </c>
       <c r="N8" s="2"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="84"/>
+      <c r="O8" s="91"/>
+      <c r="P8" s="92"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="21"/>
@@ -3023,55 +3032,55 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="84"/>
+      <c r="O9" s="91"/>
+      <c r="P9" s="92"/>
     </row>
     <row r="10" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
-      <c r="J10" s="86"/>
-      <c r="K10" s="86"/>
-      <c r="L10" s="86"/>
-      <c r="M10" s="86"/>
-      <c r="N10" s="86"/>
-      <c r="O10" s="86"/>
-      <c r="P10" s="87"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="94"/>
+      <c r="J10" s="94"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="94"/>
+      <c r="M10" s="94"/>
+      <c r="N10" s="94"/>
+      <c r="O10" s="94"/>
+      <c r="P10" s="95"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="91"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="91"/>
-      <c r="K11" s="91"/>
-      <c r="L11" s="91"/>
-      <c r="M11" s="91"/>
-      <c r="N11" s="91"/>
-      <c r="O11" s="91"/>
-      <c r="P11" s="92"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="99"/>
+      <c r="L11" s="99"/>
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="99"/>
+      <c r="P11" s="100"/>
     </row>
     <row r="12" spans="1:16" ht="20.25" customHeight="1">
-      <c r="A12" s="112" t="s">
+      <c r="A12" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="113"/>
-      <c r="C12" s="114"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="118"/>
       <c r="D12" s="15" t="s">
         <v>2</v>
       </c>
@@ -3081,11 +3090,11 @@
       <c r="F12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="115" t="s">
+      <c r="G12" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="H12" s="116"/>
-      <c r="I12" s="117"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="121"/>
       <c r="J12" s="16" t="s">
         <v>2</v>
       </c>
@@ -3109,449 +3118,453 @@
       </c>
     </row>
     <row r="13" spans="1:16" ht="15" customHeight="1">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="62" t="s">
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="63"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="118"/>
-      <c r="K13" s="118"/>
-      <c r="L13" s="118"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
       <c r="M13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="N13" s="122"/>
-      <c r="O13" s="118"/>
-      <c r="P13" s="123"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="31"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="62" t="s">
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="63"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="118"/>
-      <c r="L14" s="118"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
       <c r="M14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="N14" s="118"/>
-      <c r="O14" s="118"/>
-      <c r="P14" s="123"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="31"/>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="62" t="s">
+      <c r="B15" s="60"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="63"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="118"/>
-      <c r="L15" s="118"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
       <c r="M15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="N15" s="118"/>
-      <c r="O15" s="118"/>
-      <c r="P15" s="123"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="31"/>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="62" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="63"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="118"/>
-      <c r="L16" s="118"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
       <c r="M16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N16" s="124"/>
-      <c r="O16" s="125"/>
-      <c r="P16" s="123"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="31"/>
     </row>
     <row r="17" spans="1:17" ht="15" customHeight="1">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="62" t="s">
+      <c r="B17" s="60"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="63"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="118"/>
-      <c r="K17" s="118"/>
-      <c r="L17" s="118"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="72"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
       <c r="M17" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="N17" s="122"/>
-      <c r="O17" s="118"/>
-      <c r="P17" s="123"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="31"/>
     </row>
     <row r="18" spans="1:17" ht="15" customHeight="1">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="62" t="s">
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="63"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
       <c r="M18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N18" s="122"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="123"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="31"/>
     </row>
     <row r="19" spans="1:17" ht="15" customHeight="1">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="62" t="s">
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="63"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="118"/>
-      <c r="L19" s="118"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
       <c r="M19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="N19" s="122"/>
-      <c r="O19" s="118"/>
-      <c r="P19" s="123"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="31"/>
     </row>
     <row r="20" spans="1:17" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="62" t="s">
+      <c r="B20" s="63"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="H20" s="63"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
       <c r="M20" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="122"/>
-      <c r="O20" s="118"/>
-      <c r="P20" s="123"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="31"/>
     </row>
     <row r="21" spans="1:17" ht="15" customHeight="1">
-      <c r="A21" s="54" t="s">
+      <c r="A21" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="62" t="s">
+      <c r="B21" s="63"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="H21" s="63"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="118"/>
-      <c r="K21" s="118"/>
-      <c r="L21" s="118"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
       <c r="M21" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="122"/>
-      <c r="O21" s="118"/>
-      <c r="P21" s="123"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="31"/>
     </row>
     <row r="22" spans="1:17" ht="15" customHeight="1">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="119"/>
-      <c r="G22" s="62" t="s">
+      <c r="B22" s="65"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="63"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="118"/>
-      <c r="K22" s="118"/>
-      <c r="L22" s="118"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
       <c r="M22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="N22" s="122"/>
-      <c r="O22" s="118"/>
-      <c r="P22" s="123"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="31"/>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1">
-      <c r="A23" s="56" t="s">
+      <c r="A23" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="62" t="s">
+      <c r="B23" s="65"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="H23" s="63"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="118"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
       <c r="M23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N23" s="122"/>
-      <c r="O23" s="118"/>
-      <c r="P23" s="123"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="31"/>
       <c r="Q23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1">
-      <c r="A24" s="65" t="s">
+      <c r="A24" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="66"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="119"/>
-      <c r="G24" s="62" t="s">
+      <c r="B24" s="74"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="H24" s="63"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="118"/>
-      <c r="K24" s="118"/>
-      <c r="L24" s="118"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
       <c r="M24" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="N24" s="122"/>
-      <c r="O24" s="118"/>
-      <c r="P24" s="123"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="31"/>
     </row>
     <row r="25" spans="1:17" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="65" t="s">
+      <c r="A25" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="66"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="120"/>
-      <c r="E25" s="120"/>
-      <c r="F25" s="121"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="98"/>
-      <c r="I25" s="98"/>
-      <c r="J25" s="98"/>
-      <c r="K25" s="98"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="98"/>
-      <c r="N25" s="98"/>
-      <c r="O25" s="98"/>
-      <c r="P25" s="99"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="106"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="106"/>
+      <c r="N25" s="106"/>
+      <c r="O25" s="106"/>
+      <c r="P25" s="107"/>
     </row>
     <row r="26" spans="1:17" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A26" s="71" t="s">
+      <c r="A26" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="72"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="72"/>
-      <c r="O26" s="72"/>
-      <c r="P26" s="73"/>
-    </row>
-    <row r="27" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A27" s="100" t="s">
+      <c r="B26" s="80"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="80"/>
+      <c r="L26" s="80"/>
+      <c r="M26" s="80"/>
+      <c r="N26" s="80"/>
+      <c r="O26" s="80"/>
+      <c r="P26" s="81"/>
+    </row>
+    <row r="27" spans="1:17" ht="23.4" customHeight="1">
+      <c r="A27" s="108" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="101"/>
-      <c r="C27" s="104"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="104"/>
-      <c r="G27" s="104"/>
-      <c r="H27" s="104"/>
-      <c r="I27" s="105"/>
-      <c r="J27" s="108" t="s">
+      <c r="B27" s="109"/>
+      <c r="C27" s="122"/>
+      <c r="D27" s="122"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="122"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="112" t="s">
         <v>60</v>
       </c>
-      <c r="K27" s="108"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="104"/>
-      <c r="N27" s="104"/>
-      <c r="O27" s="104"/>
-      <c r="P27" s="110"/>
-    </row>
-    <row r="28" spans="1:17" ht="36" customHeight="1">
-      <c r="A28" s="102"/>
-      <c r="B28" s="103"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="107"/>
-      <c r="J28" s="109"/>
-      <c r="K28" s="109"/>
-      <c r="L28" s="109"/>
-      <c r="M28" s="106"/>
-      <c r="N28" s="106"/>
-      <c r="O28" s="106"/>
-      <c r="P28" s="111"/>
+      <c r="K27" s="113"/>
+      <c r="L27" s="113"/>
+      <c r="M27" s="122"/>
+      <c r="N27" s="122"/>
+      <c r="O27" s="122"/>
+      <c r="P27" s="123"/>
+    </row>
+    <row r="28" spans="1:17" ht="23.4" customHeight="1">
+      <c r="A28" s="110" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="111"/>
+      <c r="C28" s="124"/>
+      <c r="D28" s="124"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="124"/>
+      <c r="G28" s="124"/>
+      <c r="H28" s="124"/>
+      <c r="I28" s="127"/>
+      <c r="J28" s="114" t="s">
+        <v>62</v>
+      </c>
+      <c r="K28" s="115"/>
+      <c r="L28" s="115"/>
+      <c r="M28" s="124"/>
+      <c r="N28" s="124"/>
+      <c r="O28" s="124"/>
+      <c r="P28" s="125"/>
     </row>
     <row r="29" spans="1:17" s="2" customFormat="1">
-      <c r="A29" s="68" t="s">
+      <c r="A29" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="69"/>
-      <c r="L29" s="69"/>
-      <c r="M29" s="69"/>
-      <c r="N29" s="69"/>
-      <c r="O29" s="69"/>
-      <c r="P29" s="70"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="77"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="77"/>
+      <c r="L29" s="77"/>
+      <c r="M29" s="77"/>
+      <c r="N29" s="77"/>
+      <c r="O29" s="77"/>
+      <c r="P29" s="78"/>
     </row>
     <row r="30" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A30" s="43"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="44"/>
-      <c r="P30" s="45"/>
+      <c r="A30" s="51"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="52"/>
+      <c r="O30" s="52"/>
+      <c r="P30" s="53"/>
     </row>
     <row r="31" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A31" s="43"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="44"/>
-      <c r="J31" s="44"/>
-      <c r="K31" s="44"/>
-      <c r="L31" s="44"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="45"/>
-    </row>
-    <row r="32" spans="1:17" ht="13.5" thickBot="1">
-      <c r="A32" s="46"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="47"/>
-      <c r="L32" s="47"/>
-      <c r="M32" s="47"/>
-      <c r="N32" s="47"/>
-      <c r="O32" s="47"/>
-      <c r="P32" s="48"/>
+      <c r="A31" s="51"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="52"/>
+      <c r="P31" s="53"/>
+    </row>
+    <row r="32" spans="1:17" ht="13.8" thickBot="1">
+      <c r="A32" s="54"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="55"/>
+      <c r="N32" s="55"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="56"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="4"/>
@@ -3743,7 +3756,7 @@
       <c r="K44" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="56">
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="A21:C21"/>
@@ -3752,13 +3765,17 @@
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="G21:I21"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:I28"/>
-    <mergeCell ref="J27:L28"/>
-    <mergeCell ref="M27:P28"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="C28:I28"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="G22:I22"/>
     <mergeCell ref="G23:I23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A1:C3"/>
     <mergeCell ref="O4:P9"/>
     <mergeCell ref="A10:P10"/>

--- a/templates/template_inspec_excavadora.xlsx
+++ b/templates/template_inspec_excavadora.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elksi\Android\williApp\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elksi\Android\williApp\EquiposUnidos\app\src\main\res\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E68D49F-0343-475C-AD20-61DE359B5043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095FA0DD-55C9-4F1F-9019-164262942DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
     <definedName name="MENSAJEERROR2">[2]Hoja1!$D$1</definedName>
     <definedName name="MES">#REF!</definedName>
     <definedName name="PLAZO">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'FT-MANT-08'!$A$1:$P$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'FT-MANT-08'!$A$1:$P$36</definedName>
     <definedName name="TIPODEE">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
   <si>
     <t>Señale su respuesta con una ´´X´´</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>CEDULA</t>
+  </si>
+  <si>
+    <t>FIRMA</t>
   </si>
 </sst>
 </file>
@@ -558,7 +561,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="63">
+  <borders count="64">
     <border>
       <left/>
       <right/>
@@ -1308,6 +1311,17 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1375,7 +1389,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1467,6 +1481,252 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -1533,245 +1793,44 @@
     <xf numFmtId="0" fontId="25" fillId="26" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="62">
@@ -2819,7 +2878,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="1" customWidth="1"/>
@@ -2838,90 +2897,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" customHeight="1">
-      <c r="A1" s="82"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="34" t="s">
+      <c r="A1" s="61"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="36"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="115"/>
       <c r="M1" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="43" t="s">
+      <c r="N1" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="123"/>
     </row>
     <row r="2" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="39"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="118"/>
       <c r="M2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="45">
+      <c r="N2" s="124">
         <v>9</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="125"/>
     </row>
     <row r="3" spans="1:16" ht="25.5" customHeight="1">
-      <c r="A3" s="88"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="42"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="121"/>
       <c r="M3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="47">
+      <c r="N3" s="126">
         <v>45219</v>
       </c>
-      <c r="O3" s="47"/>
-      <c r="P3" s="48"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="127"/>
     </row>
     <row r="4" spans="1:16" ht="6.75" customHeight="1">
-      <c r="A4" s="103"/>
-      <c r="B4" s="104"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="104"/>
+      <c r="A4" s="91"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="92"/>
       <c r="N4" s="13"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="92"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="71"/>
     </row>
     <row r="5" spans="1:16" ht="20.25" customHeight="1">
       <c r="A5" s="21"/>
@@ -2929,23 +2988,23 @@
       <c r="C5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="96" t="s">
+      <c r="D5" s="81"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
       <c r="M5" s="24" t="s">
         <v>4</v>
       </c>
       <c r="N5" s="23"/>
-      <c r="O5" s="91"/>
-      <c r="P5" s="92"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="71"/>
     </row>
     <row r="6" spans="1:16" ht="20.25" customHeight="1">
       <c r="A6" s="21"/>
@@ -2953,23 +3012,23 @@
       <c r="C6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="101" t="s">
+      <c r="D6" s="81"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
       <c r="M6" s="24" t="s">
         <v>4</v>
       </c>
       <c r="N6" s="2"/>
-      <c r="O6" s="91"/>
-      <c r="P6" s="92"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="71"/>
     </row>
     <row r="7" spans="1:16" ht="20.25" customHeight="1">
       <c r="A7" s="21"/>
@@ -2977,21 +3036,21 @@
       <c r="C7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="57" t="s">
+      <c r="D7" s="81"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
       <c r="M7" s="25"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="91"/>
-      <c r="P7" s="92"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="71"/>
     </row>
     <row r="8" spans="1:16" ht="20.25" customHeight="1">
       <c r="A8" s="21"/>
@@ -2999,23 +3058,23 @@
       <c r="C8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="49" t="s">
+      <c r="D8" s="81"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
+      <c r="J8" s="129"/>
+      <c r="K8" s="129"/>
+      <c r="L8" s="129"/>
       <c r="M8" s="24" t="s">
         <v>4</v>
       </c>
       <c r="N8" s="2"/>
-      <c r="O8" s="91"/>
-      <c r="P8" s="92"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="71"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="21"/>
@@ -3032,55 +3091,55 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="91"/>
-      <c r="P9" s="92"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
     </row>
     <row r="10" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A10" s="93" t="s">
+      <c r="A10" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="94"/>
-      <c r="O10" s="94"/>
-      <c r="P10" s="95"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="74"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="98" t="s">
+      <c r="A11" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="99"/>
-      <c r="K11" s="99"/>
-      <c r="L11" s="99"/>
-      <c r="M11" s="99"/>
-      <c r="N11" s="99"/>
-      <c r="O11" s="99"/>
-      <c r="P11" s="100"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="87"/>
+      <c r="K11" s="87"/>
+      <c r="L11" s="87"/>
+      <c r="M11" s="87"/>
+      <c r="N11" s="87"/>
+      <c r="O11" s="87"/>
+      <c r="P11" s="88"/>
     </row>
     <row r="12" spans="1:16" ht="20.25" customHeight="1">
-      <c r="A12" s="116" t="s">
+      <c r="A12" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="117"/>
-      <c r="C12" s="118"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="15" t="s">
         <v>2</v>
       </c>
@@ -3090,11 +3149,11 @@
       <c r="F12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="119" t="s">
+      <c r="G12" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H12" s="120"/>
-      <c r="I12" s="121"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="41"/>
       <c r="J12" s="16" t="s">
         <v>2</v>
       </c>
@@ -3118,19 +3177,19 @@
       </c>
     </row>
     <row r="13" spans="1:16" ht="15" customHeight="1">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
       <c r="D13" s="26"/>
       <c r="E13" s="26"/>
       <c r="F13" s="27"/>
-      <c r="G13" s="70" t="s">
+      <c r="G13" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="71"/>
-      <c r="I13" s="72"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
       <c r="L13" s="26"/>
@@ -3142,19 +3201,19 @@
       <c r="P13" s="31"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
       <c r="D14" s="26"/>
       <c r="E14" s="26"/>
       <c r="F14" s="27"/>
-      <c r="G14" s="70" t="s">
+      <c r="G14" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="71"/>
-      <c r="I14" s="72"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="46"/>
       <c r="J14" s="26"/>
       <c r="K14" s="26"/>
       <c r="L14" s="26"/>
@@ -3166,19 +3225,19 @@
       <c r="P14" s="31"/>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="61"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="98"/>
       <c r="D15" s="26"/>
       <c r="E15" s="26"/>
       <c r="F15" s="27"/>
-      <c r="G15" s="70" t="s">
+      <c r="G15" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="71"/>
-      <c r="I15" s="72"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="46"/>
       <c r="J15" s="26"/>
       <c r="K15" s="26"/>
       <c r="L15" s="26"/>
@@ -3190,19 +3249,19 @@
       <c r="P15" s="31"/>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="61"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="98"/>
       <c r="D16" s="26"/>
       <c r="E16" s="26"/>
       <c r="F16" s="27"/>
-      <c r="G16" s="70" t="s">
+      <c r="G16" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="71"/>
-      <c r="I16" s="72"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="46"/>
       <c r="J16" s="26"/>
       <c r="K16" s="26"/>
       <c r="L16" s="26"/>
@@ -3214,19 +3273,19 @@
       <c r="P16" s="31"/>
     </row>
     <row r="17" spans="1:17" ht="15" customHeight="1">
-      <c r="A17" s="59" t="s">
+      <c r="A17" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="61"/>
+      <c r="B17" s="97"/>
+      <c r="C17" s="98"/>
       <c r="D17" s="26"/>
       <c r="E17" s="26"/>
       <c r="F17" s="27"/>
-      <c r="G17" s="70" t="s">
+      <c r="G17" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="71"/>
-      <c r="I17" s="72"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="46"/>
       <c r="J17" s="26"/>
       <c r="K17" s="26"/>
       <c r="L17" s="26"/>
@@ -3238,19 +3297,19 @@
       <c r="P17" s="31"/>
     </row>
     <row r="18" spans="1:17" ht="15" customHeight="1">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
       <c r="D18" s="26"/>
       <c r="E18" s="26"/>
       <c r="F18" s="27"/>
-      <c r="G18" s="70" t="s">
+      <c r="G18" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="71"/>
-      <c r="I18" s="72"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="46"/>
       <c r="J18" s="26"/>
       <c r="K18" s="26"/>
       <c r="L18" s="26"/>
@@ -3262,19 +3321,19 @@
       <c r="P18" s="31"/>
     </row>
     <row r="19" spans="1:17" ht="15" customHeight="1">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
       <c r="D19" s="26"/>
       <c r="E19" s="26"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="70" t="s">
+      <c r="G19" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="71"/>
-      <c r="I19" s="72"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="46"/>
       <c r="J19" s="26"/>
       <c r="K19" s="26"/>
       <c r="L19" s="26"/>
@@ -3286,19 +3345,19 @@
       <c r="P19" s="31"/>
     </row>
     <row r="20" spans="1:17" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A20" s="62" t="s">
+      <c r="A20" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
       <c r="F20" s="27"/>
-      <c r="G20" s="70" t="s">
+      <c r="G20" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="H20" s="71"/>
-      <c r="I20" s="72"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="46"/>
       <c r="J20" s="26"/>
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
@@ -3310,19 +3369,19 @@
       <c r="P20" s="31"/>
     </row>
     <row r="21" spans="1:17" ht="15" customHeight="1">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="63"/>
-      <c r="C21" s="63"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
       <c r="F21" s="27"/>
-      <c r="G21" s="70" t="s">
+      <c r="G21" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="H21" s="71"/>
-      <c r="I21" s="72"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="46"/>
       <c r="J21" s="26"/>
       <c r="K21" s="26"/>
       <c r="L21" s="26"/>
@@ -3334,19 +3393,19 @@
       <c r="P21" s="31"/>
     </row>
     <row r="22" spans="1:17" ht="15" customHeight="1">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="65"/>
-      <c r="C22" s="66"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="77"/>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
       <c r="F22" s="27"/>
-      <c r="G22" s="70" t="s">
+      <c r="G22" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="71"/>
-      <c r="I22" s="72"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="46"/>
       <c r="J22" s="26"/>
       <c r="K22" s="26"/>
       <c r="L22" s="26"/>
@@ -3358,19 +3417,19 @@
       <c r="P22" s="31"/>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1">
-      <c r="A23" s="64" t="s">
+      <c r="A23" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="66"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="77"/>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
       <c r="F23" s="27"/>
-      <c r="G23" s="70" t="s">
+      <c r="G23" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="H23" s="71"/>
-      <c r="I23" s="72"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="46"/>
       <c r="J23" s="26"/>
       <c r="K23" s="26"/>
       <c r="L23" s="26"/>
@@ -3385,19 +3444,19 @@
       </c>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1">
-      <c r="A24" s="73" t="s">
+      <c r="A24" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="74"/>
-      <c r="C24" s="75"/>
+      <c r="B24" s="79"/>
+      <c r="C24" s="80"/>
       <c r="D24" s="26"/>
       <c r="E24" s="26"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="70" t="s">
+      <c r="G24" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="H24" s="71"/>
-      <c r="I24" s="72"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="46"/>
       <c r="J24" s="26"/>
       <c r="K24" s="26"/>
       <c r="L24" s="26"/>
@@ -3409,228 +3468,240 @@
       <c r="P24" s="31"/>
     </row>
     <row r="25" spans="1:17" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="73" t="s">
+      <c r="A25" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="74"/>
-      <c r="C25" s="75"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="80"/>
       <c r="D25" s="28"/>
       <c r="E25" s="28"/>
       <c r="F25" s="29"/>
-      <c r="G25" s="105"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="106"/>
-      <c r="N25" s="106"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="107"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="94"/>
+      <c r="J25" s="94"/>
+      <c r="K25" s="94"/>
+      <c r="L25" s="94"/>
+      <c r="M25" s="94"/>
+      <c r="N25" s="94"/>
+      <c r="O25" s="94"/>
+      <c r="P25" s="95"/>
     </row>
     <row r="26" spans="1:17" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A26" s="79" t="s">
+      <c r="A26" s="110" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="80"/>
-      <c r="C26" s="80"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="80"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="80"/>
-      <c r="L26" s="80"/>
-      <c r="M26" s="80"/>
-      <c r="N26" s="80"/>
-      <c r="O26" s="80"/>
-      <c r="P26" s="81"/>
+      <c r="B26" s="111"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="111"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="111"/>
+      <c r="L26" s="111"/>
+      <c r="M26" s="111"/>
+      <c r="N26" s="111"/>
+      <c r="O26" s="111"/>
+      <c r="P26" s="112"/>
     </row>
     <row r="27" spans="1:17" ht="23.4" customHeight="1">
-      <c r="A27" s="108" t="s">
+      <c r="A27" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="109"/>
-      <c r="C27" s="122"/>
-      <c r="D27" s="122"/>
-      <c r="E27" s="122"/>
-      <c r="F27" s="122"/>
-      <c r="G27" s="122"/>
-      <c r="H27" s="122"/>
-      <c r="I27" s="126"/>
-      <c r="J27" s="112" t="s">
+      <c r="B27" s="58"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="K27" s="113"/>
-      <c r="L27" s="113"/>
-      <c r="M27" s="122"/>
-      <c r="N27" s="122"/>
-      <c r="O27" s="122"/>
-      <c r="P27" s="123"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="51"/>
+      <c r="P27" s="52"/>
     </row>
     <row r="28" spans="1:17" ht="23.4" customHeight="1">
-      <c r="A28" s="110" t="s">
+      <c r="A28" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="111"/>
-      <c r="C28" s="124"/>
-      <c r="D28" s="124"/>
-      <c r="E28" s="124"/>
-      <c r="F28" s="124"/>
-      <c r="G28" s="124"/>
-      <c r="H28" s="124"/>
-      <c r="I28" s="127"/>
-      <c r="J28" s="114" t="s">
+      <c r="B28" s="60"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="K28" s="115"/>
-      <c r="L28" s="115"/>
-      <c r="M28" s="124"/>
-      <c r="N28" s="124"/>
-      <c r="O28" s="124"/>
-      <c r="P28" s="125"/>
-    </row>
-    <row r="29" spans="1:17" s="2" customFormat="1">
-      <c r="A29" s="76" t="s">
+      <c r="K28" s="50"/>
+      <c r="L28" s="50"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="54"/>
+    </row>
+    <row r="29" spans="1:17" ht="6" customHeight="1">
+      <c r="A29" s="130"/>
+      <c r="B29" s="131"/>
+      <c r="C29" s="140"/>
+      <c r="D29" s="140"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="140"/>
+      <c r="I29" s="141"/>
+      <c r="J29" s="133"/>
+      <c r="K29" s="133"/>
+      <c r="L29" s="133"/>
+      <c r="M29" s="132"/>
+      <c r="N29" s="132"/>
+      <c r="O29" s="132"/>
+      <c r="P29" s="134"/>
+    </row>
+    <row r="30" spans="1:17" ht="33" customHeight="1">
+      <c r="A30" s="135" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="136"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="138"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="138"/>
+      <c r="G30" s="138"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="142"/>
+      <c r="J30" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="K30" s="137"/>
+      <c r="L30" s="137"/>
+      <c r="M30" s="138"/>
+      <c r="N30" s="138"/>
+      <c r="O30" s="138"/>
+      <c r="P30" s="139"/>
+    </row>
+    <row r="31" spans="1:17" ht="28.2" customHeight="1">
+      <c r="A31" s="130"/>
+      <c r="B31" s="131"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="142"/>
+      <c r="J31" s="133"/>
+      <c r="K31" s="133"/>
+      <c r="L31" s="133"/>
+      <c r="M31" s="138"/>
+      <c r="N31" s="138"/>
+      <c r="O31" s="138"/>
+      <c r="P31" s="139"/>
+    </row>
+    <row r="32" spans="1:17" ht="6" customHeight="1">
+      <c r="A32" s="130"/>
+      <c r="B32" s="131"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="133"/>
+      <c r="K32" s="133"/>
+      <c r="L32" s="133"/>
+      <c r="M32" s="132"/>
+      <c r="N32" s="132"/>
+      <c r="O32" s="132"/>
+      <c r="P32" s="134"/>
+    </row>
+    <row r="33" spans="1:16" s="2" customFormat="1">
+      <c r="A33" s="107" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="77"/>
-      <c r="C29" s="77"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="77"/>
-      <c r="K29" s="77"/>
-      <c r="L29" s="77"/>
-      <c r="M29" s="77"/>
-      <c r="N29" s="77"/>
-      <c r="O29" s="77"/>
-      <c r="P29" s="78"/>
-    </row>
-    <row r="30" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A30" s="51"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="52"/>
-      <c r="O30" s="52"/>
-      <c r="P30" s="53"/>
-    </row>
-    <row r="31" spans="1:17" ht="12.75" customHeight="1">
-      <c r="A31" s="51"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="52"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="52"/>
-      <c r="P31" s="53"/>
-    </row>
-    <row r="32" spans="1:17" ht="13.8" thickBot="1">
-      <c r="A32" s="54"/>
-      <c r="B32" s="55"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="55"/>
-      <c r="J32" s="55"/>
-      <c r="K32" s="55"/>
-      <c r="L32" s="55"/>
-      <c r="M32" s="55"/>
-      <c r="N32" s="55"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="56"/>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="B33" s="108"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="108"/>
+      <c r="E33" s="108"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="108"/>
+      <c r="H33" s="108"/>
+      <c r="I33" s="108"/>
+      <c r="J33" s="108"/>
+      <c r="K33" s="108"/>
+      <c r="L33" s="108"/>
+      <c r="M33" s="108"/>
+      <c r="N33" s="108"/>
+      <c r="O33" s="108"/>
+      <c r="P33" s="109"/>
+    </row>
+    <row r="34" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A34" s="99"/>
+      <c r="B34" s="100"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="100"/>
+      <c r="G34" s="100"/>
+      <c r="H34" s="100"/>
+      <c r="I34" s="100"/>
+      <c r="J34" s="100"/>
+      <c r="K34" s="100"/>
+      <c r="L34" s="100"/>
+      <c r="M34" s="100"/>
+      <c r="N34" s="100"/>
+      <c r="O34" s="100"/>
+      <c r="P34" s="101"/>
+    </row>
+    <row r="35" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A35" s="99"/>
+      <c r="B35" s="100"/>
+      <c r="C35" s="100"/>
+      <c r="D35" s="100"/>
+      <c r="E35" s="100"/>
+      <c r="F35" s="100"/>
+      <c r="G35" s="100"/>
+      <c r="H35" s="100"/>
+      <c r="I35" s="100"/>
+      <c r="J35" s="100"/>
+      <c r="K35" s="100"/>
+      <c r="L35" s="100"/>
+      <c r="M35" s="100"/>
+      <c r="N35" s="100"/>
+      <c r="O35" s="100"/>
+      <c r="P35" s="101"/>
+    </row>
+    <row r="36" spans="1:16" ht="13.8" thickBot="1">
+      <c r="A36" s="102"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="103"/>
+      <c r="H36" s="103"/>
+      <c r="I36" s="103"/>
+      <c r="J36" s="103"/>
+      <c r="K36" s="103"/>
+      <c r="L36" s="103"/>
+      <c r="M36" s="103"/>
+      <c r="N36" s="103"/>
+      <c r="O36" s="103"/>
+      <c r="P36" s="104"/>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -3646,7 +3717,7 @@
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:16">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -3662,7 +3733,7 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:16">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -3678,7 +3749,7 @@
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:16">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -3694,7 +3765,7 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:16">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -3710,7 +3781,7 @@
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:16">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -3726,7 +3797,7 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:16">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -3742,7 +3813,7 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:16">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -3754,29 +3825,97 @@
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="56">
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="M27:P27"/>
-    <mergeCell ref="M28:P28"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A1:C3"/>
+  <mergeCells count="60">
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="C30:I31"/>
+    <mergeCell ref="M30:P31"/>
+    <mergeCell ref="A34:P36"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A33:P33"/>
+    <mergeCell ref="A26:P26"/>
     <mergeCell ref="O4:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="A22:C22"/>
@@ -3792,27 +3931,27 @@
     <mergeCell ref="G25:P25"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A30:P32"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A29:P29"/>
-    <mergeCell ref="A26:P26"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A1:C3"/>
     <mergeCell ref="D1:L3"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="A20:C20"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
